--- a/cuadros/MAYO/SAN DIEGO.xlsx
+++ b/cuadros/MAYO/SAN DIEGO.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -64,7 +64,7 @@
     <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
   </si>
   <si>
-    <t>788</t>
+    <t>000788</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -94,13 +94,16 @@
     <t>LA "PITAHAYA" NO PERTENECE A ESTA RECEPCION</t>
   </si>
   <si>
-    <t>ERROR EN TARA DE "OCUMO CRIOLLO"</t>
+    <t>ERROR EN TARA DE "OCUMO CRIOLLO", SE COLOCO EL PESO DE LA TARA EN 2.2KG SIENDO ESTE DE 2.5KG, 0.3KG DE DIFERENCIA POR 7 TARAS PARA UN TOTAL DE 2.1KG POR 1.41$ EL KILO DE OCUMO CRIOLLO</t>
   </si>
   <si>
     <t>SIN FOTO</t>
   </si>
   <si>
     <t>NINGUNA</t>
+  </si>
+  <si>
+    <t>RECUPERACIÓN</t>
   </si>
   <si>
     <t>20260504104933</t>
@@ -520,7 +523,7 @@
         <v>28</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -552,16 +555,16 @@
         <v>26</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="s">
         <v>27</v>
       </c>
       <c r="L3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/SAN DIEGO.xlsx
+++ b/cuadros/MAYO/SAN DIEGO.xlsx
@@ -1,136 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>PROVEEDOR</t>
-  </si>
-  <si>
-    <t>FACTURA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>TIPO FISCALIZACIÓN</t>
-  </si>
-  <si>
-    <t>RESPONSABLE</t>
-  </si>
-  <si>
-    <t>INCIDENCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE ERROR</t>
-  </si>
-  <si>
-    <t>OBSERVACIÓN</t>
-  </si>
-  <si>
-    <t>MONTO $</t>
-  </si>
-  <si>
-    <t>F COBRADA</t>
-  </si>
-  <si>
-    <t>CLASIFICACIÓN MONTO</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>SAN DIEGO</t>
-  </si>
-  <si>
-    <t>AGROPECUARIA LATIN FRUITS C.A.</t>
-  </si>
-  <si>
-    <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
-  </si>
-  <si>
-    <t>000788</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>RECEPCION</t>
-  </si>
-  <si>
-    <t>SPCP Aura Machado</t>
-  </si>
-  <si>
-    <t>SPCP Neyeska Duque</t>
-  </si>
-  <si>
-    <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
-  </si>
-  <si>
-    <t>ERROR DE KG EN TARA.</t>
-  </si>
-  <si>
-    <t>TIPO C</t>
-  </si>
-  <si>
-    <t>LA "PITAHAYA" NO PERTENECE A ESTA RECEPCION</t>
-  </si>
-  <si>
-    <t>ERROR EN TARA DE "OCUMO CRIOLLO", SE COLOCO EL PESO DE LA TARA EN 2.2KG SIENDO ESTE DE 2.5KG, 0.3KG DE DIFERENCIA POR 7 TARAS PARA UN TOTAL DE 2.1KG POR 1.41$ EL KILO DE OCUMO CRIOLLO</t>
-  </si>
-  <si>
-    <t>SIN FOTO</t>
-  </si>
-  <si>
-    <t>NINGUNA</t>
-  </si>
-  <si>
-    <t>RECUPERACIÓN</t>
-  </si>
-  <si>
-    <t>20260504104933</t>
-  </si>
-  <si>
-    <t>20260504105200</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -145,14 +52,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -440,134 +415,274 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SUCURSAL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TIPO FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>INCIDENCIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TIPO DE ERROR</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MONTO $</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>F COBRADA</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CLASIFICACIÓN MONTO</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FOTO_INCIDENCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA LATIN FRUITS C.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>6482</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SPCP Aura Machado</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>LA "PITAHAYA" NO PERTENECE A ESTA RECEPCION</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>SIN FOTO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>20260504104933</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>788</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SPCP Neyeska Duque</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ERROR EN TARA DE "OCUMO CRIOLLO", SE COLOCO EL PESO DE LA TARA EN 2.2KG SIENDO ESTE DE 2.5KG, 0.3KG DE DIFERENCIA POR 7 TARAS PARA UN TOTAL DE 2.1KG POR 1.41$ EL KILO DE OCUMO CRIOLLO</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>RECUPERACIÓN</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>20260504105200</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2">
-        <v>6482</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>000703</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SPCP NELSON DE FREITAS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Se duplico el SKU de la Naranja Criolla por fallas con el Internet en tienda.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260506093937</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/SAN DIEGO.xlsx
+++ b/cuadros/MAYO/SAN DIEGO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,10 +628,8 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>000703</t>
-        </is>
+      <c r="C4" t="n">
+        <v>703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -679,6 +677,197 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>ID_20260506093937</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INVERSIONES AGROPECUARIA JEANDAVID, C.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>18494</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SPCP NELSON DE FREITAS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>EL NÚMERO DE CONTROL COLOCADO EN EL SISTEMA ES INCORRECTO, EL CORRECTO ES: 00067594</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ID_20260511142536</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6009</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SUB GERENTE CARLOS ALMENAR</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AL MOMENTO DE FIRMAR LA FACTURA EL SPCP NO COLOCO SU CÉDULA</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260511143716</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INVERSIONES VELANDRIA, C.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0059301</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SUB GERENTE CARLOS ALMENAR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EL NÚMERO DE FACTURA INGRESADO EN EL SISTEMA ES INCORRECTO, EL CORRECTO ES: 007351</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ID_20260511145506</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/SAN DIEGO.xlsx
+++ b/cuadros/MAYO/SAN DIEGO.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -57,7 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -420,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,8 +505,10 @@
           <t>AGROPECUARIA LATIN FRUITS C.A.</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>6482</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6482</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -567,8 +568,10 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>788</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -628,8 +631,10 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>703</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -691,8 +696,10 @@
           <t>INVERSIONES AGROPECUARIA JEANDAVID, C.A.</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>18494</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>18494</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -754,8 +761,10 @@
           <t>CAVA LUXOR</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>6009</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6009</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -871,7 +880,340 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13669</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SPCP IRENE E. AULAR</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EL "CALABACIN AMARILLO LARGO" NO PERTENECE A ESTA RECEPCIÓN, FUE AGREGADO POR ERROR._x000D_
+_x000D_
+</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ID_20260514153847</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SUB GERENTE YELITXA  ANGULO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SE CARGO UN DOCUMENTO QUE NO PERTENECE A ESTA RECEPCIÓN</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ID_20260514154022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>300010288</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SUB GERENTE YELITXA A. ANGULO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EL NÚMERO DE CONTROL COLOCADO EN LA APLICACIÓN ES INCORRECTO, EL CORRECTO ES: 300016288_x000D_
+_x000D_
+</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ID_20260514154146</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>300016367</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SUB GERENTE YELITXA ANGULO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE CARGO UN DOCUMENTO QUE NO PERTENECE A ESTA RECEPCIÓN_x000D_
+_x000D_
+</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ID_20260514154248</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA Y FERREAGRO SANTOS 7</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>00002825</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>YELITXA A. ANGULO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EL NÚMERO DE FACTURA COLOCADO EN LA APLICACIÓN ES INCORRECTO, EL CORRECTO ES: 00002725_x000D_
+_x000D_
+</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ID_20260514154348</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/SAN DIEGO.xlsx
+++ b/cuadros/MAYO/SAN DIEGO.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1210,6 +1210,71 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>ID_20260514154348</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>300016420</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>GERENTE JHOAN VENA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EL GERENTE DEJO EL PROCESO DE RECEPCIÓN EN ESTADO "LIBERADA" Y EL SISTEMA ELIMINO LA FACTURA AUTOMATICAMENTE A LAS 11:50PM</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ID_20260515163522</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/SAN DIEGO.xlsx
+++ b/cuadros/MAYO/SAN DIEGO.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1275,6 +1275,71 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>ID_20260515163522</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>025635</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>JHOAN VENA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LA "ACELGA COMPUESTOS DEL CAMPO 200GR" SE DUPLICO EN EL SISTEMA.</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ID_20260515165109</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/SAN DIEGO.xlsx
+++ b/cuadros/MAYO/SAN DIEGO.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1340,6 +1340,71 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>ID_20260515165109</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>025635</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>GERENTE JHOAN VENA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FALTO AGREGAR EL "COMPUESTO CEBOLLIN/CILANTRO" EN EL SISTEMA DE FISCALIZACIÓN.</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ID_20260515165223</t>
         </is>
       </c>
     </row>
